--- a/app/samples/certificate-template-4-sample.xlsx
+++ b/app/samples/certificate-template-4-sample.xlsx
@@ -397,13 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
     <col min="3" max="3" width="24.83203125" customWidth="1"/>
     <col min="4" max="4" width="24.83203125" customWidth="1"/>
     <col min="5" max="5" width="24.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -422,6 +423,9 @@
       <c r="E1" t="str">
         <v>End Date</v>
       </c>
+      <c r="F1" t="str">
+        <v>Statement</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -439,6 +443,9 @@
       <c r="E2" t="str">
         <v>16.06.2026</v>
       </c>
+      <c r="F2" t="str">
+        <v>კურსის წარმატებით დასრულებისთვის</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -456,10 +463,13 @@
       <c r="E3" t="str">
         <v>01.07.2026</v>
       </c>
+      <c r="F3" t="str">
+        <v>კურსის წარმატებით დასრულებისთვის</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/app/samples/certificate-template-4-sample.xlsx
+++ b/app/samples/certificate-template-4-sample.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -405,6 +405,7 @@
     <col min="4" max="4" width="24.83203125" customWidth="1"/>
     <col min="5" max="5" width="24.83203125" customWidth="1"/>
     <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,6 +427,9 @@
       <c r="F1" t="str">
         <v>Statement</v>
       </c>
+      <c r="G1" t="str">
+        <v>Heading (პერიოდი/თარიღი)</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -446,6 +450,9 @@
       <c r="F2" t="str">
         <v>კურსის წარმატებით დასრულებისთვის</v>
       </c>
+      <c r="G2" t="str">
+        <v>პერიოდი</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -466,10 +473,13 @@
       <c r="F3" t="str">
         <v>კურსის წარმატებით დასრულებისთვის</v>
       </c>
+      <c r="G3" t="str">
+        <v>თარიღი</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
   </ignoredErrors>
 </worksheet>
 </file>